--- a/VerveStacks_EGY_grids_kan10/SuppXLS/Scen_TSParameters_ts_12t.xlsx
+++ b/VerveStacks_EGY_grids_kan10/SuppXLS/Scen_TSParameters_ts_12t.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_EGY_grids_kan10\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5C06872E-226D-4B2E-AAA2-D9ADF9B51AD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{86226157-301F-40B0-B3E1-53487478CF7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -819,10 +819,10 @@
     <t>day_night</t>
   </si>
   <si>
-    <t>SaD,FaP,SaP,FaD,RaD,WaD,RaP,WaP</t>
+    <t>FaP,SaP,FaD,RaP,WaD,SaD,WaP,RaD</t>
   </si>
   <si>
-    <t>FaP,SaP,RaP,SaN,WaN,FaN,RaN,WaP</t>
+    <t>SaN,WaN,RaP,WaP,FaP,SaP,RaN,FaN</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -1417,7 +1417,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>FaP,SaP,RaP,SaN,WaN,FaN,RaN,WaP</v>
+        <v>SaN,WaN,RaP,WaP,FaP,SaP,RaN,FaN</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -1449,7 +1449,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>SaD,FaP,SaP,FaD,RaD,WaD,RaP,WaP</v>
+        <v>FaP,SaP,FaD,RaP,WaD,SaD,WaP,RaD</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -1545,7 +1545,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F51C1A7-E428-432A-A770-51D814A8DCC3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7267EE97-5CC8-44F5-89C8-0E20A94DA920}">
   <dimension ref="A9:G14"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1629,7 +1629,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B8D073F-3643-485C-98D7-84D0995752CF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46767F4A-4B6E-466C-992B-4287232CDA4B}">
   <dimension ref="B9:O478"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -15731,7 +15731,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BDB255C-E8D1-4D78-BFF8-BE3AF581E75E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3445DA2-1E2B-4A74-9321-9A0A4A4A6942}">
   <dimension ref="B9:BL101"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -24839,7 +24839,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D218C49B-E992-42B4-9152-5FF5EA32FA03}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04293298-9D90-4FEB-8FD0-E9E835F976C6}">
   <dimension ref="B9:E22"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -25037,7 +25037,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1EB39B0-CBFE-41F8-941A-E676E8075AA7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4624F26-A52C-4C1A-AAE3-82A3737C55EB}">
   <dimension ref="B9:D34"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -25328,7 +25328,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02005AFD-39C6-4652-89B9-DF567747A9B2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1203C061-13D5-46C5-91EA-002C18B5B9B6}">
   <dimension ref="B9:D22"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -25487,7 +25487,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E063F41A-A24B-4808-8583-F2FF1D5BA25B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4A17FDF-D569-49D1-854A-5536B5080633}">
   <dimension ref="B9:E126"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -25547,7 +25547,7 @@
         <v>43</v>
       </c>
       <c r="D13">
-        <v>0.86606666666666665</v>
+        <v>0.86606666666666676</v>
       </c>
       <c r="E13" t="s">
         <v>266</v>
@@ -25589,7 +25589,7 @@
         <v>41</v>
       </c>
       <c r="D16">
-        <v>0.65400000000000003</v>
+        <v>0.65399999999999991</v>
       </c>
       <c r="E16" t="s">
         <v>266</v>
@@ -25603,7 +25603,7 @@
         <v>43</v>
       </c>
       <c r="D17">
-        <v>0.84803333333333342</v>
+        <v>0.84803333333333331</v>
       </c>
       <c r="E17" t="s">
         <v>266</v>
@@ -25673,7 +25673,7 @@
         <v>45</v>
       </c>
       <c r="D22">
-        <v>0.41543333333333332</v>
+        <v>0.41543333333333338</v>
       </c>
       <c r="E22" t="s">
         <v>266</v>
@@ -25869,7 +25869,7 @@
         <v>41</v>
       </c>
       <c r="D36">
-        <v>0.67540000000000011</v>
+        <v>0.67539999999999989</v>
       </c>
       <c r="E36" t="s">
         <v>266</v>
@@ -25883,7 +25883,7 @@
         <v>43</v>
       </c>
       <c r="D37">
-        <v>0.78216666666666657</v>
+        <v>0.78216666666666679</v>
       </c>
       <c r="E37" t="s">
         <v>266</v>
@@ -25939,7 +25939,7 @@
         <v>43</v>
       </c>
       <c r="D41">
-        <v>0.7636666666666666</v>
+        <v>0.76366666666666683</v>
       </c>
       <c r="E41" t="s">
         <v>266</v>
@@ -25981,7 +25981,7 @@
         <v>41</v>
       </c>
       <c r="D44">
-        <v>0.61099999999999999</v>
+        <v>0.61099999999999988</v>
       </c>
       <c r="E44" t="s">
         <v>266</v>
@@ -26023,7 +26023,7 @@
         <v>37</v>
       </c>
       <c r="D47">
-        <v>0.47023333333333334</v>
+        <v>0.47023333333333328</v>
       </c>
       <c r="E47" t="s">
         <v>266</v>
@@ -26065,7 +26065,7 @@
         <v>45</v>
       </c>
       <c r="D50">
-        <v>0.37469999999999998</v>
+        <v>0.37470000000000003</v>
       </c>
       <c r="E50" t="s">
         <v>266</v>
@@ -26079,7 +26079,7 @@
         <v>37</v>
       </c>
       <c r="D51">
-        <v>0.45976666666666671</v>
+        <v>0.45976666666666666</v>
       </c>
       <c r="E51" t="s">
         <v>266</v>
@@ -26233,7 +26233,7 @@
         <v>45</v>
       </c>
       <c r="D62">
-        <v>0.44116666666666671</v>
+        <v>0.44116666666666665</v>
       </c>
       <c r="E62" t="s">
         <v>266</v>
@@ -26261,7 +26261,7 @@
         <v>41</v>
       </c>
       <c r="D64">
-        <v>0.68200000000000005</v>
+        <v>0.68199999999999994</v>
       </c>
       <c r="E64" t="s">
         <v>266</v>
@@ -26387,7 +26387,7 @@
         <v>43</v>
       </c>
       <c r="D73">
-        <v>0.8026333333333332</v>
+        <v>0.80263333333333342</v>
       </c>
       <c r="E73" t="s">
         <v>266</v>
@@ -26429,7 +26429,7 @@
         <v>41</v>
       </c>
       <c r="D76">
-        <v>0.66046666666666665</v>
+        <v>0.66046666666666676</v>
       </c>
       <c r="E76" t="s">
         <v>266</v>
@@ -26597,7 +26597,7 @@
         <v>41</v>
       </c>
       <c r="D88">
-        <v>0.61870000000000003</v>
+        <v>0.61869999999999992</v>
       </c>
       <c r="E88" t="s">
         <v>266</v>
@@ -26639,7 +26639,7 @@
         <v>37</v>
       </c>
       <c r="D91">
-        <v>0.51473333333333327</v>
+        <v>0.51473333333333338</v>
       </c>
       <c r="E91" t="s">
         <v>266</v>
@@ -26667,7 +26667,7 @@
         <v>43</v>
       </c>
       <c r="D93">
-        <v>0.71476666666666677</v>
+        <v>0.71476666666666666</v>
       </c>
       <c r="E93" t="s">
         <v>266</v>
@@ -26681,7 +26681,7 @@
         <v>45</v>
       </c>
       <c r="D94">
-        <v>0.37656666666666672</v>
+        <v>0.37656666666666666</v>
       </c>
       <c r="E94" t="s">
         <v>266</v>
@@ -26709,7 +26709,7 @@
         <v>41</v>
       </c>
       <c r="D96">
-        <v>0.54996666666666671</v>
+        <v>0.5499666666666666</v>
       </c>
       <c r="E96" t="s">
         <v>266</v>
@@ -26779,7 +26779,7 @@
         <v>43</v>
       </c>
       <c r="D101">
-        <v>0.72253333333333325</v>
+        <v>0.72253333333333336</v>
       </c>
       <c r="E101" t="s">
         <v>266</v>
@@ -26905,7 +26905,7 @@
         <v>45</v>
       </c>
       <c r="D110">
-        <v>0.38203333333333339</v>
+        <v>0.38203333333333328</v>
       </c>
       <c r="E110" t="s">
         <v>266</v>
@@ -27045,7 +27045,7 @@
         <v>41</v>
       </c>
       <c r="D120">
-        <v>0.60013333333333341</v>
+        <v>0.6001333333333333</v>
       </c>
       <c r="E120" t="s">
         <v>266</v>
@@ -27059,7 +27059,7 @@
         <v>43</v>
       </c>
       <c r="D121">
-        <v>0.67903333333333327</v>
+        <v>0.67903333333333338</v>
       </c>
       <c r="E121" t="s">
         <v>266</v>
@@ -27073,7 +27073,7 @@
         <v>45</v>
       </c>
       <c r="D122">
-        <v>0.34916666666666668</v>
+        <v>0.34916666666666663</v>
       </c>
       <c r="E122" t="s">
         <v>266</v>
